--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA531E1-0824-4159-B6F7-8C4AE706B353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FD4FD3-F7E8-45B3-8E67-195D7E1C3E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="195" windowWidth="10860" windowHeight="10785" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="8385" yWindow="135" windowWidth="10860" windowHeight="10785" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -440,41 +440,65 @@
       <c r="B3" t="s">
         <v>2</v>
       </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>5</v>
       </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>6</v>
       </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>8</v>
       </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>9</v>
       </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -484,6 +508,9 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FD4FD3-F7E8-45B3-8E67-195D7E1C3E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4401DE4-0192-4AFD-A1C2-50BCB606C51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="135" windowWidth="10860" windowHeight="10785" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="9525" yWindow="0" windowWidth="10860" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Antigua</t>
   </si>
@@ -69,6 +69,75 @@
   </si>
   <si>
     <t>pcrit 2 viernes</t>
+  </si>
+  <si>
+    <t>31 secc</t>
+  </si>
+  <si>
+    <t>Baldeon Toribio Yadira</t>
+  </si>
+  <si>
+    <t>Calderón José Andrés</t>
+  </si>
+  <si>
+    <t>Coronado Sofía</t>
+  </si>
+  <si>
+    <t>De la Cruz Belen</t>
+  </si>
+  <si>
+    <t>Diaz Briana</t>
+  </si>
+  <si>
+    <t>Fabian Julinho</t>
+  </si>
+  <si>
+    <t>Huanuco Flor</t>
+  </si>
+  <si>
+    <t>Leon Johanny</t>
+  </si>
+  <si>
+    <t>Lizaraso Kenjy</t>
+  </si>
+  <si>
+    <t>Martel Mirella</t>
+  </si>
+  <si>
+    <t>Palomino Naylea</t>
+  </si>
+  <si>
+    <t>Vargas Flavianna</t>
+  </si>
+  <si>
+    <t>33 secc</t>
+  </si>
+  <si>
+    <t>Acosta Maria Fernanda</t>
+  </si>
+  <si>
+    <t>Bacilio Andrey</t>
+  </si>
+  <si>
+    <t>Cordova Paola</t>
+  </si>
+  <si>
+    <t>Duran Luzana</t>
+  </si>
+  <si>
+    <t>Garcia Belissa</t>
+  </si>
+  <si>
+    <t>Gutierrez Flor</t>
+  </si>
+  <si>
+    <t>Narcizo Lucia</t>
+  </si>
+  <si>
+    <t>Sosa Ana Karina</t>
+  </si>
+  <si>
+    <t>pc1</t>
   </si>
 </sst>
 </file>
@@ -504,6 +573,9 @@
       <c r="B11" t="s">
         <v>10</v>
       </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -520,12 +592,124 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2E3F7E-AE67-4335-8010-6E79C40D1EEE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -535,12 +719,87 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD31480-9EA2-4F3F-9175-5B0745D87526}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4401DE4-0192-4AFD-A1C2-50BCB606C51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5932B709-9FDB-44FC-A33D-10E260AB5644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9525" yWindow="0" windowWidth="10860" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Antigua</t>
   </si>
@@ -65,12 +65,6 @@
     <t>Silva Juan Miguel</t>
   </si>
   <si>
-    <t>pcrit 1 juev</t>
-  </si>
-  <si>
-    <t>pcrit 2 viernes</t>
-  </si>
-  <si>
     <t>31 secc</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
     <t>Vargas Flavianna</t>
   </si>
   <si>
-    <t>33 secc</t>
-  </si>
-  <si>
     <t>Acosta Maria Fernanda</t>
   </si>
   <si>
@@ -138,6 +129,21 @@
   </si>
   <si>
     <t>pc1</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>Promedio</t>
+  </si>
+  <si>
+    <t>Debate</t>
+  </si>
+  <si>
+    <t>pcrit jueves</t>
+  </si>
+  <si>
+    <t>pcrit viernes</t>
   </si>
 </sst>
 </file>
@@ -489,23 +495,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E647F6D9-36F0-4B5C-9F0F-9318A90F4048}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -513,15 +525,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -529,7 +541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -537,7 +549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -545,7 +557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -553,7 +565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -561,7 +573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -569,7 +581,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>10</v>
       </c>
@@ -577,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -592,124 +604,166 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2E3F7E-AE67-4335-8010-6E79C40D1EEE}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C5">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
       <c r="C6">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
       <c r="C9">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="C13">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>22</v>
-      </c>
-      <c r="C12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>24</v>
       </c>
       <c r="C14">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>14</v>
+      </c>
+      <c r="D16">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -719,87 +773,111 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD31480-9EA2-4F3F-9175-5B0745D87526}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>29</v>
-      </c>
-      <c r="C4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>32</v>
       </c>
       <c r="C7">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>18</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5932B709-9FDB-44FC-A33D-10E260AB5644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCC3092-3C02-4AE6-B74E-C65EC143DF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="9630" yWindow="135" windowWidth="10860" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>Garcia Belissa</t>
   </si>
   <si>
-    <t>Gutierrez Flor</t>
-  </si>
-  <si>
     <t>Narcizo Lucia</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>pcrit viernes</t>
+  </si>
+  <si>
+    <t>Gutierrez Flor Melene</t>
   </si>
 </sst>
 </file>
@@ -511,10 +511,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
         <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -612,7 +612,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
         <v>12</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -697,7 +697,7 @@
         <v>17</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -781,15 +781,15 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -849,7 +849,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>17</v>
@@ -860,7 +860,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>17</v>
@@ -871,7 +871,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>18</v>

--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCC3092-3C02-4AE6-B74E-C65EC143DF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4781EEFC-69F5-4DF7-8D99-07B118FB1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9630" yWindow="135" windowWidth="10860" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="390" yWindow="135" windowWidth="8085" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/registro de numeros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4781EEFC-69F5-4DF7-8D99-07B118FB1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84233A01-60D6-4FCE-9A5F-B961BF34AB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="135" windowWidth="8085" windowHeight="10785" activeTab="2" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
+    <workbookView xWindow="9405" yWindow="0" windowWidth="10695" windowHeight="10920" xr2:uid="{903916D8-322A-4327-8325-78D5B3C538BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -524,6 +524,9 @@
       <c r="C3">
         <v>16</v>
       </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -532,6 +535,9 @@
       <c r="C4">
         <v>17</v>
       </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -540,6 +546,9 @@
       <c r="C5">
         <v>16</v>
       </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -548,6 +557,9 @@
       <c r="C6">
         <v>17</v>
       </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -556,6 +568,9 @@
       <c r="C7">
         <v>14</v>
       </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -564,6 +579,9 @@
       <c r="C8">
         <v>18</v>
       </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -572,6 +590,9 @@
       <c r="C9">
         <v>18</v>
       </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -580,6 +601,9 @@
       <c r="C10">
         <v>14</v>
       </c>
+      <c r="D10">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -588,6 +612,9 @@
       <c r="C11">
         <v>15</v>
       </c>
+      <c r="D11">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -595,6 +622,9 @@
       </c>
       <c r="C12">
         <v>17</v>
+      </c>
+      <c r="D12">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -604,13 +634,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2E3F7E-AE67-4335-8010-6E79C40D1EEE}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -618,7 +648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>32</v>
       </c>
@@ -626,7 +656,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -636,8 +666,11 @@
       <c r="D4">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -647,8 +680,11 @@
       <c r="D5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -658,16 +694,16 @@
       <c r="D6">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -677,8 +713,11 @@
       <c r="D8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -688,8 +727,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -699,8 +741,11 @@
       <c r="D10">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -710,8 +755,11 @@
       <c r="D11">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>20</v>
       </c>
@@ -721,8 +769,11 @@
       <c r="D12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>21</v>
       </c>
@@ -732,8 +783,11 @@
       <c r="D13">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>22</v>
       </c>
@@ -743,8 +797,11 @@
       <c r="D14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>23</v>
       </c>
@@ -754,8 +811,11 @@
       <c r="D15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -764,6 +824,9 @@
       </c>
       <c r="D16">
         <v>13</v>
+      </c>
+      <c r="E16">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -773,18 +836,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD31480-9EA2-4F3F-9175-5B0745D87526}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>32</v>
       </c>
@@ -792,7 +855,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>25</v>
       </c>
@@ -802,8 +865,11 @@
       <c r="D3">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -813,8 +879,11 @@
       <c r="D4">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>27</v>
       </c>
@@ -824,8 +893,11 @@
       <c r="D5">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>28</v>
       </c>
@@ -835,8 +907,11 @@
       <c r="D6">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -846,8 +921,11 @@
       <c r="D7">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -857,8 +935,11 @@
       <c r="D8">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>30</v>
       </c>
@@ -868,8 +949,11 @@
       <c r="D9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -878,6 +962,9 @@
       </c>
       <c r="D10">
         <v>15</v>
+      </c>
+      <c r="E10">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
